--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4952,7 +4952,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>167</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -10604,7 +10604,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>281</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$171</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5300" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5330" uniqueCount="450">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -913,6 +913,12 @@
   </si>
   <si>
     <t>AssignedEntity.code</t>
+  </si>
+  <si>
+    <t>Supply.performer.assignedEntity.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcSpecialty</t>
   </si>
   <si>
     <t>Supply.performer.assignedEntity.addr</t>
@@ -1728,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK170"/>
+  <dimension ref="A1:AK171"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="85.8828125" customWidth="true" bestFit="true"/>
@@ -10931,7 +10937,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>291</v>
+        <v>180</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10984,7 +10990,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -11004,10 +11010,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11030,7 +11036,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -11083,7 +11089,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -11103,10 +11109,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11117,7 +11123,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>74</v>
@@ -11129,7 +11135,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11182,13 +11188,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>74</v>
@@ -11202,18 +11208,16 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E94" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
@@ -11230,12 +11234,10 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>85</v>
+        <v>299</v>
       </c>
       <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11261,11 +11263,13 @@
         <v>74</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z94" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>74</v>
@@ -11283,7 +11287,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>89</v>
+        <v>300</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11303,21 +11307,23 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -11329,11 +11335,11 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11360,13 +11366,11 @@
         <v>74</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>74</v>
@@ -11384,13 +11388,13 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>74</v>
@@ -11404,10 +11408,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11418,7 +11422,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>74</v>
@@ -11430,11 +11434,11 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11485,19 +11489,19 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>74</v>
@@ -11505,18 +11509,16 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E97" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
@@ -11533,11 +11535,11 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11564,11 +11566,13 @@
         <v>74</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11586,7 +11590,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11598,7 +11602,7 @@
         <v>74</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>74</v>
@@ -11606,17 +11610,17 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>80</v>
@@ -11634,11 +11638,11 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11665,13 +11669,11 @@
         <v>74</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>74</v>
@@ -11689,7 +11691,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11709,17 +11711,17 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>80</v>
@@ -11737,11 +11739,11 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11792,7 +11794,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11812,20 +11814,20 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>75</v>
@@ -11840,11 +11842,11 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11853,7 +11855,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>74</v>
@@ -11895,7 +11897,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11915,17 +11917,17 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>75</v>
@@ -11943,11 +11945,11 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11956,7 +11958,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>74</v>
@@ -11998,7 +12000,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -12018,21 +12020,23 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>74</v>
@@ -12044,11 +12048,11 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12099,13 +12103,13 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>74</v>
@@ -12119,10 +12123,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12133,7 +12137,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>74</v>
@@ -12145,10 +12149,12 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -12156,7 +12162,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>309</v>
+        <v>74</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>74</v>
@@ -12174,11 +12180,13 @@
         <v>74</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>310</v>
+        <v>74</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -12196,13 +12204,13 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>311</v>
+        <v>125</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>74</v>
@@ -12216,10 +12224,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12253,7 +12261,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>74</v>
@@ -12275,7 +12283,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>74</v>
@@ -12293,7 +12301,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12313,10 +12321,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12324,7 +12332,7 @@
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>75</v>
@@ -12339,7 +12347,7 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>317</v>
+        <v>85</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
@@ -12350,7 +12358,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>74</v>
+        <v>315</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>74</v>
@@ -12368,13 +12376,11 @@
         <v>74</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>74</v>
+        <v>316</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>74</v>
@@ -12392,13 +12398,13 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>74</v>
@@ -12412,10 +12418,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12423,7 +12429,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>75</v>
@@ -12438,12 +12444,10 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>174</v>
+        <v>319</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12493,13 +12497,13 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>74</v>
@@ -12513,10 +12517,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12527,7 +12531,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>74</v>
@@ -12539,11 +12543,11 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12594,13 +12598,13 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>74</v>
@@ -12614,23 +12618,21 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E108" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>74</v>
@@ -12642,11 +12644,11 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>86</v>
+        <v>325</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12673,11 +12675,13 @@
         <v>74</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -12695,13 +12699,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>89</v>
+        <v>326</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12715,21 +12719,23 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>74</v>
@@ -12741,11 +12747,11 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -12772,13 +12778,11 @@
         <v>74</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -12796,13 +12800,13 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>74</v>
@@ -12816,10 +12820,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12830,7 +12834,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -12842,11 +12846,11 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12897,19 +12901,19 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>74</v>
@@ -12917,18 +12921,16 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E111" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
@@ -12945,11 +12947,11 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12976,11 +12978,13 @@
         <v>74</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y111" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>74</v>
@@ -12998,7 +13002,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13010,7 +13014,7 @@
         <v>74</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>74</v>
@@ -13018,17 +13022,17 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F112" t="s" s="2">
         <v>80</v>
@@ -13046,11 +13050,11 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -13077,13 +13081,11 @@
         <v>74</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>74</v>
@@ -13101,7 +13103,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13121,17 +13123,17 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F113" t="s" s="2">
         <v>80</v>
@@ -13149,11 +13151,11 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13204,7 +13206,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13224,20 +13226,20 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>75</v>
@@ -13252,11 +13254,11 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13265,7 +13267,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>74</v>
@@ -13307,7 +13309,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13327,17 +13329,17 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>75</v>
@@ -13355,11 +13357,11 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13368,7 +13370,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>74</v>
@@ -13410,7 +13412,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13430,21 +13432,23 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F116" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>74</v>
@@ -13456,11 +13460,11 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13511,13 +13515,13 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>74</v>
@@ -13531,10 +13535,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13542,10 +13546,10 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>74</v>
@@ -13557,10 +13561,12 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L117" s="2"/>
-      <c r="M117" s="2"/>
+      <c r="M117" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -13568,7 +13574,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>335</v>
+        <v>74</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>74</v>
@@ -13610,13 +13616,13 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>336</v>
+        <v>125</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>74</v>
@@ -13630,10 +13636,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13641,7 +13647,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>75</v>
@@ -13667,7 +13673,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>74</v>
@@ -13712,7 +13718,7 @@
         <v>338</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>75</v>
@@ -13740,7 +13746,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>75</v>
@@ -13755,7 +13761,7 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
@@ -13766,7 +13772,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>74</v>
+        <v>315</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>74</v>
@@ -13811,7 +13817,7 @@
         <v>340</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>75</v>
@@ -13839,7 +13845,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>75</v>
@@ -13854,7 +13860,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>342</v>
+        <v>180</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13907,10 +13913,10 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>75</v>
@@ -13927,18 +13933,16 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E121" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>80</v>
       </c>
@@ -13955,12 +13959,10 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>85</v>
+        <v>344</v>
       </c>
       <c r="L121" s="2"/>
-      <c r="M121" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M121" s="2"/>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -13986,11 +13988,13 @@
         <v>74</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y121" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z121" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>74</v>
@@ -14008,7 +14012,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>89</v>
+        <v>345</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14028,21 +14032,23 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E122" s="2"/>
+      <c r="E122" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>74</v>
@@ -14054,11 +14060,11 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -14085,13 +14091,11 @@
         <v>74</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>74</v>
@@ -14109,13 +14113,13 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>74</v>
@@ -14129,10 +14133,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14143,7 +14147,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>74</v>
@@ -14155,11 +14159,11 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14210,19 +14214,19 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>74</v>
@@ -14230,18 +14234,16 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E124" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
@@ -14258,11 +14260,11 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14289,11 +14291,13 @@
         <v>74</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y124" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z124" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>74</v>
@@ -14311,7 +14315,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14323,7 +14327,7 @@
         <v>74</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>74</v>
@@ -14331,17 +14335,17 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F125" t="s" s="2">
         <v>80</v>
@@ -14359,11 +14363,11 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14390,13 +14394,11 @@
         <v>74</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>74</v>
@@ -14414,7 +14416,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14434,17 +14436,17 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F126" t="s" s="2">
         <v>80</v>
@@ -14462,11 +14464,11 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14517,7 +14519,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14537,20 +14539,20 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F127" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>75</v>
@@ -14565,11 +14567,11 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14578,7 +14580,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>74</v>
@@ -14620,7 +14622,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14640,17 +14642,17 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F128" t="s" s="2">
         <v>75</v>
@@ -14668,11 +14670,11 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14681,7 +14683,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>74</v>
@@ -14723,7 +14725,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14743,21 +14745,23 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E129" s="2"/>
+      <c r="E129" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F129" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>74</v>
@@ -14769,11 +14773,11 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14824,13 +14828,13 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>74</v>
@@ -14844,10 +14848,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14858,7 +14862,7 @@
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>74</v>
@@ -14870,10 +14874,12 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L130" s="2"/>
-      <c r="M130" s="2"/>
+      <c r="M130" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -14881,7 +14887,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>354</v>
+        <v>74</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>74</v>
@@ -14899,11 +14905,13 @@
         <v>74</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y130" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z130" t="s" s="2">
-        <v>355</v>
+        <v>74</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>74</v>
@@ -14921,13 +14929,13 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>356</v>
+        <v>125</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>74</v>
@@ -14941,10 +14949,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14978,7 +14986,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>313</v>
+        <v>356</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>74</v>
@@ -15000,7 +15008,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>74</v>
@@ -15052,7 +15060,7 @@
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>74</v>
@@ -15064,7 +15072,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15075,7 +15083,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>74</v>
+        <v>315</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>74</v>
@@ -15093,13 +15101,11 @@
         <v>74</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>74</v>
+        <v>316</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>74</v>
@@ -15123,7 +15129,7 @@
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>74</v>
@@ -15148,10 +15154,10 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>74</v>
@@ -15163,7 +15169,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>362</v>
+        <v>95</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15216,7 +15222,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15236,10 +15242,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15247,10 +15253,10 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>74</v>
@@ -15262,7 +15268,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>294</v>
+        <v>364</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15361,7 +15367,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15448,7 +15454,7 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>74</v>
@@ -15460,7 +15466,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>180</v>
+        <v>293</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15489,35 +15495,37 @@
         <v>74</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y136" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF136" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AA136" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>74</v>
@@ -15531,10 +15539,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15557,7 +15565,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>372</v>
+        <v>180</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -15586,13 +15594,11 @@
         <v>74</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>74</v>
+        <v>371</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>74</v>
@@ -15610,7 +15616,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15630,10 +15636,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15656,7 +15662,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -15709,7 +15715,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15729,10 +15735,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15740,7 +15746,7 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>75</v>
@@ -15755,7 +15761,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>95</v>
+        <v>377</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -15811,7 +15817,7 @@
         <v>378</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>75</v>
@@ -15839,7 +15845,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>75</v>
@@ -15854,7 +15860,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>380</v>
+        <v>95</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -15907,13 +15913,13 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>74</v>
@@ -15941,7 +15947,7 @@
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>74</v>
@@ -16123,7 +16129,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
         <v>385</v>
       </c>
@@ -16142,7 +16148,7 @@
         <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>74</v>
@@ -16153,9 +16159,7 @@
       <c r="K143" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L143" t="s" s="2">
-        <v>387</v>
-      </c>
+      <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16224,28 +16228,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E144" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>74</v>
@@ -16254,12 +16256,12 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L144" s="2"/>
-      <c r="M144" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -16285,11 +16287,13 @@
         <v>74</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y144" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z144" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>74</v>
@@ -16307,13 +16311,13 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>89</v>
+        <v>387</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>74</v>
@@ -16327,21 +16331,23 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E145" s="2"/>
+      <c r="E145" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>74</v>
@@ -16353,11 +16359,11 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -16384,13 +16390,11 @@
         <v>74</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>74</v>
@@ -16408,13 +16412,13 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>74</v>
@@ -16428,10 +16432,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16442,7 +16446,7 @@
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>74</v>
@@ -16454,11 +16458,11 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -16509,19 +16513,19 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>74</v>
@@ -16529,18 +16533,16 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E147" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>80</v>
       </c>
@@ -16557,11 +16559,11 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -16588,11 +16590,13 @@
         <v>74</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y147" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z147" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>74</v>
@@ -16610,7 +16614,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -16622,7 +16626,7 @@
         <v>74</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>74</v>
@@ -16630,17 +16634,17 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F148" t="s" s="2">
         <v>80</v>
@@ -16658,11 +16662,11 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -16689,13 +16693,11 @@
         <v>74</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -16713,7 +16715,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -16733,17 +16735,17 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F149" t="s" s="2">
         <v>80</v>
@@ -16761,11 +16763,11 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -16816,7 +16818,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -16836,20 +16838,20 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F150" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>75</v>
@@ -16864,11 +16866,11 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -16877,7 +16879,7 @@
       </c>
       <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S150" t="s" s="2">
         <v>74</v>
@@ -16919,7 +16921,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -16939,17 +16941,17 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F151" t="s" s="2">
         <v>75</v>
@@ -16967,11 +16969,11 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -16980,7 +16982,7 @@
       </c>
       <c r="Q151" s="2"/>
       <c r="R151" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S151" t="s" s="2">
         <v>74</v>
@@ -17022,7 +17024,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17042,21 +17044,23 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E152" s="2"/>
+      <c r="E152" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F152" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>74</v>
@@ -17068,11 +17072,11 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17123,13 +17127,13 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>74</v>
@@ -17143,10 +17147,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17154,10 +17158,10 @@
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>74</v>
@@ -17169,10 +17173,12 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L153" s="2"/>
-      <c r="M153" s="2"/>
+      <c r="M153" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -17183,7 +17189,7 @@
         <v>74</v>
       </c>
       <c r="S153" t="s" s="2">
-        <v>398</v>
+        <v>74</v>
       </c>
       <c r="T153" t="s" s="2">
         <v>74</v>
@@ -17198,11 +17204,13 @@
         <v>74</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y153" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z153" t="s" s="2">
-        <v>399</v>
+        <v>74</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>74</v>
@@ -17220,13 +17228,13 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>400</v>
+        <v>125</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>74</v>
@@ -17240,10 +17248,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17251,7 +17259,7 @@
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>75</v>
@@ -17266,12 +17274,10 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L154" s="2"/>
-      <c r="M154" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="M154" s="2"/>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -17282,7 +17288,7 @@
         <v>74</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>74</v>
+        <v>400</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>74</v>
@@ -17297,13 +17303,11 @@
         <v>74</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>74</v>
+        <v>401</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>74</v>
@@ -17321,10 +17325,10 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>75</v>
@@ -17341,10 +17345,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17371,12 +17375,12 @@
       </c>
       <c r="L155" s="2"/>
       <c r="M155" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
-        <v>406</v>
+        <v>74</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
@@ -17422,7 +17426,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17442,10 +17446,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17471,11 +17475,13 @@
         <v>107</v>
       </c>
       <c r="L156" s="2"/>
-      <c r="M156" s="2"/>
+      <c r="M156" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
-        <v>74</v>
+        <v>408</v>
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
@@ -17567,7 +17573,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>411</v>
+        <v>107</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17620,7 +17626,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -17640,10 +17646,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17666,7 +17672,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>186</v>
+        <v>413</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -17765,7 +17771,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>416</v>
+        <v>186</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17818,7 +17824,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -17838,10 +17844,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17864,7 +17870,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -17917,7 +17923,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -17937,10 +17943,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -17963,7 +17969,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18016,7 +18022,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18036,10 +18042,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18062,7 +18068,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18115,7 +18121,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18135,10 +18141,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18161,7 +18167,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18214,7 +18220,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18234,10 +18240,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18260,7 +18266,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18313,7 +18319,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18333,10 +18339,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18359,7 +18365,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18412,7 +18418,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18432,10 +18438,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18458,7 +18464,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -18511,7 +18517,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -18531,10 +18537,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18557,7 +18563,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -18610,7 +18616,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -18630,10 +18636,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18644,7 +18650,7 @@
         <v>80</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>74</v>
@@ -18656,7 +18662,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -18709,13 +18715,13 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>74</v>
@@ -18925,8 +18931,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L171" s="2"/>
+      <c r="M171" s="2"/>
+      <c r="N171" s="2"/>
+      <c r="O171" s="2"/>
+      <c r="P171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK170">
+  <autoFilter ref="A1:AK171">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18936,7 +19041,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI169">
+  <conditionalFormatting sqref="A2:AI170">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-prescription.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
